--- a/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
+++ b/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hugo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4F9A8B-8342-4978-94A7-3FD880638099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775E2871-40D3-4561-8EAC-1482108E01FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -151,12 +151,6 @@
 pour suivi des VCS</t>
   </si>
   <si>
-    <t>BeSafe: Application web permettant de gérer les visites comportementales de sécurité</t>
-  </si>
-  <si>
-    <t>Klimarine: Application web pour laquage dans la chaine de production</t>
-  </si>
-  <si>
     <t>01/01/2026
 au
 ?</t>
@@ -167,14 +161,22 @@
 ?</t>
   </si>
   <si>
-    <t>26/05/2025 
+    <t>Klimarine: Application web pour gestion qualimarine pour laquage dans la chaine
+de production</t>
+  </si>
+  <si>
+    <t>26/05/2025
 au
 04/07/2025</t>
   </si>
   <si>
-    <t>04/07/2025
-au
-26/08/2025</t>
+    <t>07/07/2025
+au 
+28/08/2025</t>
+  </si>
+  <si>
+    <t>BeSafe: Application web permettant de gérer les visites comportementales
+de sécurité (VCS)</t>
   </si>
 </sst>
 </file>
@@ -775,7 +777,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -813,6 +815,63 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -876,13 +935,37 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -891,58 +974,10 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1178,67 +1213,66 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AH83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
     <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="43" width="11.42578125" customWidth="1"/>
-    <col min="44" max="16384" width="10.85546875" style="1"/>
+    <col min="9" max="34" width="11.42578125" customWidth="1"/>
+    <col min="35" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+    <row r="1" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="32" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13" t="s">
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="13"/>
-    </row>
-    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="H1" s="32"/>
+    </row>
+    <row r="2" spans="1:34" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+      <c r="D2" s="32"/>
+      <c r="E2" s="32"/>
+      <c r="F2" s="32"/>
+      <c r="G2" s="32"/>
+      <c r="H2" s="32"/>
+    </row>
+    <row r="3" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17" t="s">
+      <c r="B3" s="34"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="35"/>
+      <c r="F3" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="18"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="37"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-    </row>
-    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+    </row>
+    <row r="4" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
+      <c r="B4" s="42"/>
+      <c r="C4" s="42"/>
+      <c r="D4" s="42"/>
+      <c r="E4" s="43"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1249,23 +1283,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+    <row r="5" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="44" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="27"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="s">
+      <c r="B5" s="45"/>
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="45"/>
+      <c r="F5" s="45"/>
+      <c r="G5" s="45"/>
+      <c r="H5" s="46"/>
+    </row>
+    <row r="6" spans="1:34" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="49" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1287,9 +1321,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:43" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29"/>
-      <c r="B7" s="31"/>
+    <row r="7" spans="1:34" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="48"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
@@ -1334,27 +1368,18 @@
       <c r="AF7"/>
       <c r="AG7"/>
       <c r="AH7"/>
-      <c r="AI7"/>
-      <c r="AJ7"/>
-      <c r="AK7"/>
-      <c r="AL7"/>
-      <c r="AM7"/>
-      <c r="AN7"/>
-      <c r="AO7"/>
-      <c r="AP7"/>
-      <c r="AQ7"/>
-    </row>
-    <row r="8" spans="1:43" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="32" t="s">
+    </row>
+    <row r="8" spans="1:34" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="53"/>
+      <c r="H8" s="54"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1381,29 +1406,20 @@
       <c r="AF8"/>
       <c r="AG8"/>
       <c r="AH8"/>
-      <c r="AI8"/>
-      <c r="AJ8"/>
-      <c r="AK8"/>
-      <c r="AL8"/>
-      <c r="AM8"/>
-      <c r="AN8"/>
-      <c r="AO8"/>
-      <c r="AP8"/>
-      <c r="AQ8"/>
-    </row>
-    <row r="9" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="37" t="s">
+    </row>
+    <row r="9" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="46" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
+      <c r="B9" s="60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="62"/>
+      <c r="D9" s="66"/>
+      <c r="E9" s="55"/>
+      <c r="F9" s="55"/>
+      <c r="G9" s="55"/>
+      <c r="H9" s="55"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1430,25 +1446,16 @@
       <c r="AF9"/>
       <c r="AG9"/>
       <c r="AH9"/>
-      <c r="AI9"/>
-      <c r="AJ9"/>
-      <c r="AK9"/>
-      <c r="AL9"/>
-      <c r="AM9"/>
-      <c r="AN9"/>
-      <c r="AO9"/>
-      <c r="AP9"/>
-      <c r="AQ9"/>
-    </row>
-    <row r="10" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="38"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
+    </row>
+    <row r="10" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="65"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="63"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="56"/>
+      <c r="F10" s="56"/>
+      <c r="G10" s="56"/>
+      <c r="H10" s="56"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1475,29 +1482,20 @@
       <c r="AF10"/>
       <c r="AG10"/>
       <c r="AH10"/>
-      <c r="AI10"/>
-      <c r="AJ10"/>
-      <c r="AK10"/>
-      <c r="AL10"/>
-      <c r="AM10"/>
-      <c r="AN10"/>
-      <c r="AO10"/>
-      <c r="AP10"/>
-      <c r="AQ10"/>
-    </row>
-    <row r="11" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="34" t="s">
+    </row>
+    <row r="11" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="45" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="53"/>
+      <c r="B11" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="15"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="59"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1524,25 +1522,16 @@
       <c r="AF11"/>
       <c r="AG11"/>
       <c r="AH11"/>
-      <c r="AI11"/>
-      <c r="AJ11"/>
-      <c r="AK11"/>
-      <c r="AL11"/>
-      <c r="AM11"/>
-      <c r="AN11"/>
-      <c r="AO11"/>
-      <c r="AP11"/>
-      <c r="AQ11"/>
-    </row>
-    <row r="12" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
+    </row>
+    <row r="12" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="20"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="31"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1569,27 +1558,18 @@
       <c r="AF12"/>
       <c r="AG12"/>
       <c r="AH12"/>
-      <c r="AI12"/>
-      <c r="AJ12"/>
-      <c r="AK12"/>
-      <c r="AL12"/>
-      <c r="AM12"/>
-      <c r="AN12"/>
-      <c r="AO12"/>
-      <c r="AP12"/>
-      <c r="AQ12"/>
-    </row>
-    <row r="13" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+    </row>
+    <row r="13" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="38" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="21"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="40"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1616,29 +1596,20 @@
       <c r="AF13"/>
       <c r="AG13"/>
       <c r="AH13"/>
-      <c r="AI13"/>
-      <c r="AJ13"/>
-      <c r="AK13"/>
-      <c r="AL13"/>
-      <c r="AM13"/>
-      <c r="AN13"/>
-      <c r="AO13"/>
-      <c r="AP13"/>
-      <c r="AQ13"/>
-    </row>
-    <row r="14" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="45" t="s">
+    </row>
+    <row r="14" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="24" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="56"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="29"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1665,25 +1636,16 @@
       <c r="AF14"/>
       <c r="AG14"/>
       <c r="AH14"/>
-      <c r="AI14"/>
-      <c r="AJ14"/>
-      <c r="AK14"/>
-      <c r="AL14"/>
-      <c r="AM14"/>
-      <c r="AN14"/>
-      <c r="AO14"/>
-      <c r="AP14"/>
-      <c r="AQ14"/>
-    </row>
-    <row r="15" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55"/>
+    </row>
+    <row r="15" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="25"/>
+      <c r="B15" s="28"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1710,27 +1672,20 @@
       <c r="AF15"/>
       <c r="AG15"/>
       <c r="AH15"/>
-      <c r="AI15"/>
-      <c r="AJ15"/>
-      <c r="AK15"/>
-      <c r="AL15"/>
-      <c r="AM15"/>
-      <c r="AN15"/>
-      <c r="AO15"/>
-      <c r="AP15"/>
-      <c r="AQ15"/>
-    </row>
-    <row r="16" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="21"/>
+    </row>
+    <row r="16" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="26" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="13"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1757,29 +1712,16 @@
       <c r="AF16"/>
       <c r="AG16"/>
       <c r="AH16"/>
-      <c r="AI16"/>
-      <c r="AJ16"/>
-      <c r="AK16"/>
-      <c r="AL16"/>
-      <c r="AM16"/>
-      <c r="AN16"/>
-      <c r="AO16"/>
-      <c r="AP16"/>
-      <c r="AQ16"/>
-    </row>
-    <row r="17" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="56"/>
+    </row>
+    <row r="17" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="27"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1806,25 +1748,18 @@
       <c r="AF17"/>
       <c r="AG17"/>
       <c r="AH17"/>
-      <c r="AI17"/>
-      <c r="AJ17"/>
-      <c r="AK17"/>
-      <c r="AL17"/>
-      <c r="AM17"/>
-      <c r="AN17"/>
-      <c r="AO17"/>
-      <c r="AP17"/>
-      <c r="AQ17"/>
-    </row>
-    <row r="18" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="55"/>
+    </row>
+    <row r="18" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="22"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="23"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1851,29 +1786,20 @@
       <c r="AF18"/>
       <c r="AG18"/>
       <c r="AH18"/>
-      <c r="AI18"/>
-      <c r="AJ18"/>
-      <c r="AK18"/>
-      <c r="AL18"/>
-      <c r="AM18"/>
-      <c r="AN18"/>
-      <c r="AO18"/>
-      <c r="AP18"/>
-      <c r="AQ18"/>
-    </row>
-    <row r="19" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34" t="s">
+    </row>
+    <row r="19" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="56"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="30"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1900,25 +1826,16 @@
       <c r="AF19"/>
       <c r="AG19"/>
       <c r="AH19"/>
-      <c r="AI19"/>
-      <c r="AJ19"/>
-      <c r="AK19"/>
-      <c r="AL19"/>
-      <c r="AM19"/>
-      <c r="AN19"/>
-      <c r="AO19"/>
-      <c r="AP19"/>
-      <c r="AQ19"/>
-    </row>
-    <row r="20" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="55"/>
+    </row>
+    <row r="20" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="20"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="31"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1945,25 +1862,8 @@
       <c r="AF20"/>
       <c r="AG20"/>
       <c r="AH20"/>
-      <c r="AI20"/>
-      <c r="AJ20"/>
-      <c r="AK20"/>
-      <c r="AL20"/>
-      <c r="AM20"/>
-      <c r="AN20"/>
-      <c r="AO20"/>
-      <c r="AP20"/>
-      <c r="AQ20"/>
-    </row>
-    <row r="21" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
+    </row>
+    <row r="21" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1990,25 +1890,8 @@
       <c r="AF21"/>
       <c r="AG21"/>
       <c r="AH21"/>
-      <c r="AI21"/>
-      <c r="AJ21"/>
-      <c r="AK21"/>
-      <c r="AL21"/>
-      <c r="AM21"/>
-      <c r="AN21"/>
-      <c r="AO21"/>
-      <c r="AP21"/>
-      <c r="AQ21"/>
-    </row>
-    <row r="22" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
+    </row>
+    <row r="22" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2035,17 +1918,8 @@
       <c r="AF22"/>
       <c r="AG22"/>
       <c r="AH22"/>
-      <c r="AI22"/>
-      <c r="AJ22"/>
-      <c r="AK22"/>
-      <c r="AL22"/>
-      <c r="AM22"/>
-      <c r="AN22"/>
-      <c r="AO22"/>
-      <c r="AP22"/>
-      <c r="AQ22"/>
-    </row>
-    <row r="23" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="23" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -2080,25 +1954,16 @@
       <c r="AF23"/>
       <c r="AG23"/>
       <c r="AH23"/>
-      <c r="AI23"/>
-      <c r="AJ23"/>
-      <c r="AK23"/>
-      <c r="AL23"/>
-      <c r="AM23"/>
-      <c r="AN23"/>
-      <c r="AO23"/>
-      <c r="AP23"/>
-      <c r="AQ23"/>
-    </row>
-    <row r="24" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
+    </row>
+    <row r="24" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2125,17 +1990,8 @@
       <c r="AF24"/>
       <c r="AG24"/>
       <c r="AH24"/>
-      <c r="AI24"/>
-      <c r="AJ24"/>
-      <c r="AK24"/>
-      <c r="AL24"/>
-      <c r="AM24"/>
-      <c r="AN24"/>
-      <c r="AO24"/>
-      <c r="AP24"/>
-      <c r="AQ24"/>
-    </row>
-    <row r="25" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="25" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -2170,25 +2026,16 @@
       <c r="AF25"/>
       <c r="AG25"/>
       <c r="AH25"/>
-      <c r="AI25"/>
-      <c r="AJ25"/>
-      <c r="AK25"/>
-      <c r="AL25"/>
-      <c r="AM25"/>
-      <c r="AN25"/>
-      <c r="AO25"/>
-      <c r="AP25"/>
-      <c r="AQ25"/>
-    </row>
-    <row r="26" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
+    </row>
+    <row r="26" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2215,17 +2062,8 @@
       <c r="AF26"/>
       <c r="AG26"/>
       <c r="AH26"/>
-      <c r="AI26"/>
-      <c r="AJ26"/>
-      <c r="AK26"/>
-      <c r="AL26"/>
-      <c r="AM26"/>
-      <c r="AN26"/>
-      <c r="AO26"/>
-      <c r="AP26"/>
-      <c r="AQ26"/>
-    </row>
-    <row r="27" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="27" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -2260,17 +2098,8 @@
       <c r="AF27"/>
       <c r="AG27"/>
       <c r="AH27"/>
-      <c r="AI27"/>
-      <c r="AJ27"/>
-      <c r="AK27"/>
-      <c r="AL27"/>
-      <c r="AM27"/>
-      <c r="AN27"/>
-      <c r="AO27"/>
-      <c r="AP27"/>
-      <c r="AQ27"/>
-    </row>
-    <row r="28" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="28" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
@@ -2305,17 +2134,8 @@
       <c r="AF28"/>
       <c r="AG28"/>
       <c r="AH28"/>
-      <c r="AI28"/>
-      <c r="AJ28"/>
-      <c r="AK28"/>
-      <c r="AL28"/>
-      <c r="AM28"/>
-      <c r="AN28"/>
-      <c r="AO28"/>
-      <c r="AP28"/>
-      <c r="AQ28"/>
-    </row>
-    <row r="29" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="29" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -2350,17 +2170,8 @@
       <c r="AF29"/>
       <c r="AG29"/>
       <c r="AH29"/>
-      <c r="AI29"/>
-      <c r="AJ29"/>
-      <c r="AK29"/>
-      <c r="AL29"/>
-      <c r="AM29"/>
-      <c r="AN29"/>
-      <c r="AO29"/>
-      <c r="AP29"/>
-      <c r="AQ29"/>
-    </row>
-    <row r="30" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
@@ -2395,17 +2206,8 @@
       <c r="AF30"/>
       <c r="AG30"/>
       <c r="AH30"/>
-      <c r="AI30"/>
-      <c r="AJ30"/>
-      <c r="AK30"/>
-      <c r="AL30"/>
-      <c r="AM30"/>
-      <c r="AN30"/>
-      <c r="AO30"/>
-      <c r="AP30"/>
-      <c r="AQ30"/>
-    </row>
-    <row r="31" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="31" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
@@ -2440,17 +2242,8 @@
       <c r="AF31"/>
       <c r="AG31"/>
       <c r="AH31"/>
-      <c r="AI31"/>
-      <c r="AJ31"/>
-      <c r="AK31"/>
-      <c r="AL31"/>
-      <c r="AM31"/>
-      <c r="AN31"/>
-      <c r="AO31"/>
-      <c r="AP31"/>
-      <c r="AQ31"/>
-    </row>
-    <row r="32" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="32" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
@@ -2478,8 +2271,15 @@
       <c r="Y32"/>
       <c r="Z32"/>
       <c r="AA32"/>
-    </row>
-    <row r="33" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB32"/>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32"/>
+      <c r="AF32"/>
+      <c r="AG32"/>
+      <c r="AH32"/>
+    </row>
+    <row r="33" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
@@ -2507,8 +2307,15 @@
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
-    </row>
-    <row r="34" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AB33"/>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33"/>
+      <c r="AF33"/>
+      <c r="AG33"/>
+      <c r="AH33"/>
+    </row>
+    <row r="34" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34"/>
@@ -2527,17 +2334,8 @@
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34"/>
-      <c r="S34"/>
-      <c r="T34"/>
-      <c r="U34"/>
-      <c r="V34"/>
-      <c r="W34"/>
-      <c r="X34"/>
-      <c r="Y34"/>
-      <c r="Z34"/>
-      <c r="AA34"/>
-    </row>
-    <row r="35" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="35" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -2556,45 +2354,74 @@
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35"/>
-      <c r="S35"/>
-      <c r="T35"/>
-      <c r="U35"/>
-      <c r="V35"/>
-      <c r="W35"/>
-      <c r="X35"/>
-      <c r="Y35"/>
-      <c r="Z35"/>
-      <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="36" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+    </row>
+    <row r="37" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37"/>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37"/>
+      <c r="AF37"/>
+      <c r="AG37"/>
+      <c r="AH37"/>
+    </row>
+    <row r="38" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2617,26 +2444,8 @@
     <row r="68" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="69" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-    </row>
-    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-    </row>
+    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
@@ -2727,24 +2536,40 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
+    <row r="82" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:H18"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
@@ -2755,20 +2580,16 @@
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
@@ -2776,11 +2597,19 @@
     <mergeCell ref="F14:F15"/>
     <mergeCell ref="G14:G15"/>
     <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="D19:D20"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078738" right="0.19685039370078738" top="0.19685039370078738" bottom="0.19685039370078738" header="0.51181102362204722" footer="0.51181102362204722"/>

--- a/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
+++ b/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hugo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{775E2871-40D3-4561-8EAC-1482108E01FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC04EE9C-088F-429C-8F6F-C911BA06E564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -156,11 +156,6 @@
 ?</t>
   </si>
   <si>
-    <t>12/01/2026 
-au
-?</t>
-  </si>
-  <si>
     <t>Klimarine: Application web pour gestion qualimarine pour laquage dans la chaine
 de production</t>
   </si>
@@ -177,6 +172,11 @@
   <si>
     <t>BeSafe: Application web permettant de gérer les visites comportementales
 de sécurité (VCS)</t>
+  </si>
+  <si>
+    <t>12/01/2026 
+au
+27/02/2026</t>
   </si>
 </sst>
 </file>
@@ -815,30 +815,135 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -866,118 +971,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1224,55 +1224,55 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="49" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
-      <c r="G1" s="32" t="s">
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="32"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" spans="1:34" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-      <c r="D2" s="32"/>
-      <c r="E2" s="32"/>
-      <c r="F2" s="32"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="32"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
     </row>
     <row r="3" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="35"/>
-      <c r="F3" s="36" t="s">
+      <c r="B3" s="51"/>
+      <c r="C3" s="51"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="52"/>
+      <c r="F3" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="34"/>
-      <c r="H3" s="37"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="54"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
     </row>
     <row r="4" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="41" t="s">
+      <c r="A4" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="42"/>
-      <c r="C4" s="42"/>
-      <c r="D4" s="42"/>
-      <c r="E4" s="43"/>
+      <c r="B4" s="29"/>
+      <c r="C4" s="29"/>
+      <c r="D4" s="29"/>
+      <c r="E4" s="30"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1284,22 +1284,22 @@
       </c>
     </row>
     <row r="5" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44" t="s">
+      <c r="A5" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="45"/>
-      <c r="C5" s="45"/>
-      <c r="D5" s="45"/>
-      <c r="E5" s="45"/>
-      <c r="F5" s="45"/>
-      <c r="G5" s="45"/>
-      <c r="H5" s="46"/>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="32"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="33"/>
     </row>
     <row r="6" spans="1:34" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="49" t="s">
+      <c r="B6" s="36" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1322,8 +1322,8 @@
       </c>
     </row>
     <row r="7" spans="1:34" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="48"/>
-      <c r="B7" s="50"/>
+      <c r="A7" s="35"/>
+      <c r="B7" s="37"/>
       <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
@@ -1370,16 +1370,16 @@
       <c r="AH7"/>
     </row>
     <row r="8" spans="1:34" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="38" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="54"/>
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="41"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1408,18 +1408,18 @@
       <c r="AH8"/>
     </row>
     <row r="9" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="60" t="s">
+      <c r="B9" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="62"/>
-      <c r="D9" s="66"/>
-      <c r="E9" s="55"/>
-      <c r="F9" s="55"/>
-      <c r="G9" s="55"/>
-      <c r="H9" s="55"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="23"/>
+      <c r="G9" s="23"/>
+      <c r="H9" s="23"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1448,14 +1448,14 @@
       <c r="AH9"/>
     </row>
     <row r="10" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="65"/>
-      <c r="B10" s="61"/>
-      <c r="C10" s="63"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="56"/>
-      <c r="F10" s="56"/>
-      <c r="G10" s="56"/>
-      <c r="H10" s="56"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1484,18 +1484,18 @@
       <c r="AH10"/>
     </row>
     <row r="11" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="42" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="59"/>
+      <c r="C11" s="46"/>
+      <c r="D11" s="48"/>
+      <c r="E11" s="48"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="48"/>
+      <c r="H11" s="13"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1524,14 +1524,14 @@
       <c r="AH11"/>
     </row>
     <row r="12" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="31"/>
+      <c r="A12" s="43"/>
+      <c r="B12" s="45"/>
+      <c r="C12" s="47"/>
+      <c r="D12" s="47"/>
+      <c r="E12" s="47"/>
+      <c r="F12" s="47"/>
+      <c r="G12" s="47"/>
+      <c r="H12" s="14"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1560,16 +1560,16 @@
       <c r="AH12"/>
     </row>
     <row r="13" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="25" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="39"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="40"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="26"/>
+      <c r="D13" s="26"/>
+      <c r="E13" s="26"/>
+      <c r="F13" s="26"/>
+      <c r="G13" s="26"/>
+      <c r="H13" s="27"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1598,18 +1598,18 @@
       <c r="AH13"/>
     </row>
     <row r="14" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="24" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="29"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
+      <c r="A14" s="59" t="s">
+        <v>34</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="G14" s="64"/>
+      <c r="H14" s="64"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1638,14 +1638,14 @@
       <c r="AH14"/>
     </row>
     <row r="15" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="25"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
+      <c r="A15" s="60"/>
+      <c r="B15" s="63"/>
+      <c r="C15" s="65"/>
+      <c r="D15" s="65"/>
+      <c r="E15" s="65"/>
+      <c r="F15" s="65"/>
+      <c r="G15" s="65"/>
+      <c r="H15" s="65"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1674,18 +1674,18 @@
       <c r="AH15"/>
     </row>
     <row r="16" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="B16" s="26" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
+      <c r="A16" s="61" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="61" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="65"/>
+      <c r="D16" s="65"/>
+      <c r="E16" s="65"/>
+      <c r="F16" s="65"/>
+      <c r="G16" s="65"/>
+      <c r="H16" s="65"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1714,14 +1714,14 @@
       <c r="AH16"/>
     </row>
     <row r="17" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="27"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
+      <c r="A17" s="62"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66"/>
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1750,16 +1750,16 @@
       <c r="AH17"/>
     </row>
     <row r="18" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="23"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="58"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1788,18 +1788,18 @@
       <c r="AH18"/>
     </row>
     <row r="19" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="30"/>
+      <c r="B19" s="44" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="67"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1828,14 +1828,14 @@
       <c r="AH19"/>
     </row>
     <row r="20" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="31"/>
+      <c r="A20" s="43"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="47"/>
+      <c r="D20" s="47"/>
+      <c r="E20" s="47"/>
+      <c r="F20" s="47"/>
+      <c r="G20" s="47"/>
+      <c r="H20" s="14"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2558,12 +2558,36 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="B19:B20"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A13:H13"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
@@ -2580,36 +2604,12 @@
     <mergeCell ref="E11:E12"/>
     <mergeCell ref="F11:F12"/>
     <mergeCell ref="G11:G12"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="E9:E10"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078738" right="0.19685039370078738" top="0.19685039370078738" bottom="0.19685039370078738" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2627,6 +2627,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944753b-810f-46c8-bac0-e8d58c60cb9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010056620F2C176D974991F270E01E69A174" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="c1041e1bc637f9a452b3a666f0dfb4c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c944753b-810f-46c8-bac0-e8d58c60cb9e" xmlns:ns3="4de7a12e-8c42-4030-a9c5-072174f335a6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3c11a7b616be7a4861d8d8f26cc3a83b" ns2:_="" ns3:_="">
     <xsd:import namespace="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
@@ -2843,16 +2853,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944753b-810f-46c8-bac0-e8d58c60cb9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C2B63-1469-46C2-8035-1ACD6A901C28}">
   <ds:schemaRefs>
@@ -2862,6 +2862,16 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DA88B-CC83-4B6A-8FB8-D09E146481DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A1580AE-FEAE-4C59-8F8B-C5B5168C8CA5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2878,14 +2888,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DA88B-CC83-4B6A-8FB8-D09E146481DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
+++ b/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hugo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC04EE9C-088F-429C-8F6F-C911BA06E564}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4F9A8B-8342-4978-94A7-3FD880638099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$24</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -151,32 +151,30 @@
 pour suivi des VCS</t>
   </si>
   <si>
+    <t>BeSafe: Application web permettant de gérer les visites comportementales de sécurité</t>
+  </si>
+  <si>
+    <t>Klimarine: Application web pour laquage dans la chaine de production</t>
+  </si>
+  <si>
     <t>01/01/2026
 au
 ?</t>
   </si>
   <si>
-    <t>Klimarine: Application web pour gestion qualimarine pour laquage dans la chaine
-de production</t>
-  </si>
-  <si>
-    <t>26/05/2025
+    <t>12/01/2026 
+au
+?</t>
+  </si>
+  <si>
+    <t>26/05/2025 
 au
 04/07/2025</t>
   </si>
   <si>
-    <t>07/07/2025
-au 
-28/08/2025</t>
-  </si>
-  <si>
-    <t>BeSafe: Application web permettant de gérer les visites comportementales
-de sécurité (VCS)</t>
-  </si>
-  <si>
-    <t>12/01/2026 
+    <t>04/07/2025
 au
-27/02/2026</t>
+26/08/2025</t>
   </si>
 </sst>
 </file>
@@ -777,7 +775,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -815,166 +813,133 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1213,66 +1178,67 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AH83"/>
+  <dimension ref="A1:AQ81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" style="1" customWidth="1"/>
     <col min="3" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="34" width="11.42578125" customWidth="1"/>
-    <col min="35" max="16384" width="10.85546875" style="1"/>
+    <col min="9" max="43" width="11.42578125" customWidth="1"/>
+    <col min="44" max="16384" width="10.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49" t="s">
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="49"/>
-    </row>
-    <row r="2" spans="1:34" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="49" t="s">
+      <c r="H1" s="13"/>
+    </row>
+    <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="49"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="49"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="49"/>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
-    </row>
-    <row r="3" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="50" t="s">
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="53" t="s">
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="51"/>
-      <c r="H3" s="54"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="18"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="28" t="s">
+      <c r="M3" s="1"/>
+    </row>
+    <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="29"/>
-      <c r="C4" s="29"/>
-      <c r="D4" s="29"/>
-      <c r="E4" s="30"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="24"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1283,23 +1249,23 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="31" t="s">
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32"/>
-      <c r="F5" s="32"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="33"/>
-    </row>
-    <row r="6" spans="1:34" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="34" t="s">
+      <c r="B5" s="26"/>
+      <c r="C5" s="26"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="27"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="36" t="s">
+      <c r="B6" s="30" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1321,9 +1287,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:34" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="35"/>
-      <c r="B7" s="37"/>
+    <row r="7" spans="1:43" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="29"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
@@ -1368,18 +1334,27 @@
       <c r="AF7"/>
       <c r="AG7"/>
       <c r="AH7"/>
-    </row>
-    <row r="8" spans="1:34" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="38" t="s">
+      <c r="AI7"/>
+      <c r="AJ7"/>
+      <c r="AK7"/>
+      <c r="AL7"/>
+      <c r="AM7"/>
+      <c r="AN7"/>
+      <c r="AO7"/>
+      <c r="AP7"/>
+      <c r="AQ7"/>
+    </row>
+    <row r="8" spans="1:43" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
+      <c r="A8" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="39"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="41"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="39"/>
+      <c r="H8" s="40"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1406,20 +1381,29 @@
       <c r="AF8"/>
       <c r="AG8"/>
       <c r="AH8"/>
-    </row>
-    <row r="9" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="19" t="s">
+      <c r="AI8"/>
+      <c r="AJ8"/>
+      <c r="AK8"/>
+      <c r="AL8"/>
+      <c r="AM8"/>
+      <c r="AN8"/>
+      <c r="AO8"/>
+      <c r="AP8"/>
+      <c r="AQ8"/>
+    </row>
+    <row r="9" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="17"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="23"/>
-      <c r="H9" s="23"/>
+      <c r="B9" s="46" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="41"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="43"/>
+      <c r="G9" s="43"/>
+      <c r="H9" s="43"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1446,16 +1430,25 @@
       <c r="AF9"/>
       <c r="AG9"/>
       <c r="AH9"/>
-    </row>
-    <row r="10" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="24"/>
-      <c r="F10" s="24"/>
-      <c r="G10" s="24"/>
-      <c r="H10" s="24"/>
+      <c r="AI9"/>
+      <c r="AJ9"/>
+      <c r="AK9"/>
+      <c r="AL9"/>
+      <c r="AM9"/>
+      <c r="AN9"/>
+      <c r="AO9"/>
+      <c r="AP9"/>
+      <c r="AQ9"/>
+    </row>
+    <row r="10" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="38"/>
+      <c r="B10" s="47"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="44"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="44"/>
+      <c r="H10" s="44"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1482,20 +1475,29 @@
       <c r="AF10"/>
       <c r="AG10"/>
       <c r="AH10"/>
-    </row>
-    <row r="11" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="42" t="s">
+      <c r="AI10"/>
+      <c r="AJ10"/>
+      <c r="AK10"/>
+      <c r="AL10"/>
+      <c r="AM10"/>
+      <c r="AN10"/>
+      <c r="AO10"/>
+      <c r="AP10"/>
+      <c r="AQ10"/>
+    </row>
+    <row r="11" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="34" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="44" t="s">
-        <v>30</v>
-      </c>
-      <c r="C11" s="46"/>
-      <c r="D11" s="48"/>
-      <c r="E11" s="48"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="48"/>
-      <c r="H11" s="13"/>
+      <c r="B11" s="45" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="51"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="52"/>
+      <c r="G11" s="52"/>
+      <c r="H11" s="53"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1522,16 +1524,25 @@
       <c r="AF11"/>
       <c r="AG11"/>
       <c r="AH11"/>
-    </row>
-    <row r="12" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="43"/>
-      <c r="B12" s="45"/>
-      <c r="C12" s="47"/>
-      <c r="D12" s="47"/>
-      <c r="E12" s="47"/>
-      <c r="F12" s="47"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="14"/>
+      <c r="AI11"/>
+      <c r="AJ11"/>
+      <c r="AK11"/>
+      <c r="AL11"/>
+      <c r="AM11"/>
+      <c r="AN11"/>
+      <c r="AO11"/>
+      <c r="AP11"/>
+      <c r="AQ11"/>
+    </row>
+    <row r="12" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="35"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="54"/>
+      <c r="D12" s="54"/>
+      <c r="E12" s="54"/>
+      <c r="F12" s="54"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="55"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1558,18 +1569,27 @@
       <c r="AF12"/>
       <c r="AG12"/>
       <c r="AH12"/>
-    </row>
-    <row r="13" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="25" t="s">
+      <c r="AI12"/>
+      <c r="AJ12"/>
+      <c r="AK12"/>
+      <c r="AL12"/>
+      <c r="AM12"/>
+      <c r="AN12"/>
+      <c r="AO12"/>
+      <c r="AP12"/>
+      <c r="AQ12"/>
+    </row>
+    <row r="13" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-      <c r="D13" s="26"/>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="27"/>
+      <c r="B13" s="20"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="21"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1596,20 +1616,29 @@
       <c r="AF13"/>
       <c r="AG13"/>
       <c r="AH13"/>
-    </row>
-    <row r="14" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="59" t="s">
-        <v>34</v>
-      </c>
-      <c r="B14" s="59" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="64"/>
-      <c r="D14" s="64"/>
-      <c r="E14" s="64"/>
-      <c r="F14" s="64"/>
-      <c r="G14" s="64"/>
-      <c r="H14" s="64"/>
+      <c r="AI13"/>
+      <c r="AJ13"/>
+      <c r="AK13"/>
+      <c r="AL13"/>
+      <c r="AM13"/>
+      <c r="AN13"/>
+      <c r="AO13"/>
+      <c r="AP13"/>
+      <c r="AQ13"/>
+    </row>
+    <row r="14" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="45" t="s">
+        <v>33</v>
+      </c>
+      <c r="C14" s="51"/>
+      <c r="D14" s="51"/>
+      <c r="E14" s="51"/>
+      <c r="F14" s="51"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="56"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1636,16 +1665,25 @@
       <c r="AF14"/>
       <c r="AG14"/>
       <c r="AH14"/>
-    </row>
-    <row r="15" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="60"/>
-      <c r="B15" s="63"/>
-      <c r="C15" s="65"/>
-      <c r="D15" s="65"/>
-      <c r="E15" s="65"/>
-      <c r="F15" s="65"/>
-      <c r="G15" s="65"/>
-      <c r="H15" s="65"/>
+      <c r="AI14"/>
+      <c r="AJ14"/>
+      <c r="AK14"/>
+      <c r="AL14"/>
+      <c r="AM14"/>
+      <c r="AN14"/>
+      <c r="AO14"/>
+      <c r="AP14"/>
+      <c r="AQ14"/>
+    </row>
+    <row r="15" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="54"/>
+      <c r="D15" s="54"/>
+      <c r="E15" s="54"/>
+      <c r="F15" s="54"/>
+      <c r="G15" s="54"/>
+      <c r="H15" s="55"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1672,20 +1710,27 @@
       <c r="AF15"/>
       <c r="AG15"/>
       <c r="AH15"/>
-    </row>
-    <row r="16" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="61" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="61" t="s">
-        <v>33</v>
-      </c>
-      <c r="C16" s="65"/>
-      <c r="D16" s="65"/>
-      <c r="E16" s="65"/>
-      <c r="F16" s="65"/>
-      <c r="G16" s="65"/>
-      <c r="H16" s="65"/>
+      <c r="AI15"/>
+      <c r="AJ15"/>
+      <c r="AK15"/>
+      <c r="AL15"/>
+      <c r="AM15"/>
+      <c r="AN15"/>
+      <c r="AO15"/>
+      <c r="AP15"/>
+      <c r="AQ15"/>
+    </row>
+    <row r="16" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" s="20"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="20"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="21"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
@@ -1712,16 +1757,29 @@
       <c r="AF16"/>
       <c r="AG16"/>
       <c r="AH16"/>
-    </row>
-    <row r="17" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="62"/>
-      <c r="B17" s="62"/>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66"/>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
+      <c r="AI16"/>
+      <c r="AJ16"/>
+      <c r="AK16"/>
+      <c r="AL16"/>
+      <c r="AM16"/>
+      <c r="AN16"/>
+      <c r="AO16"/>
+      <c r="AP16"/>
+      <c r="AQ16"/>
+    </row>
+    <row r="17" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="B17" s="45" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" s="51"/>
+      <c r="D17" s="51"/>
+      <c r="E17" s="51"/>
+      <c r="F17" s="51"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="56"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
@@ -1748,18 +1806,25 @@
       <c r="AF17"/>
       <c r="AG17"/>
       <c r="AH17"/>
-    </row>
-    <row r="18" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="56" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="57"/>
-      <c r="C18" s="57"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
-      <c r="F18" s="57"/>
-      <c r="G18" s="57"/>
-      <c r="H18" s="58"/>
+      <c r="AI17"/>
+      <c r="AJ17"/>
+      <c r="AK17"/>
+      <c r="AL17"/>
+      <c r="AM17"/>
+      <c r="AN17"/>
+      <c r="AO17"/>
+      <c r="AP17"/>
+      <c r="AQ17"/>
+    </row>
+    <row r="18" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="35"/>
+      <c r="B18" s="36"/>
+      <c r="C18" s="54"/>
+      <c r="D18" s="54"/>
+      <c r="E18" s="54"/>
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="55"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1786,20 +1851,29 @@
       <c r="AF18"/>
       <c r="AG18"/>
       <c r="AH18"/>
-    </row>
-    <row r="19" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="42" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="44" t="s">
+      <c r="AI18"/>
+      <c r="AJ18"/>
+      <c r="AK18"/>
+      <c r="AL18"/>
+      <c r="AM18"/>
+      <c r="AN18"/>
+      <c r="AO18"/>
+      <c r="AP18"/>
+      <c r="AQ18"/>
+    </row>
+    <row r="19" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="B19" s="48" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="67"/>
+      <c r="C19" s="51"/>
+      <c r="D19" s="51"/>
+      <c r="E19" s="51"/>
+      <c r="F19" s="51"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="56"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1826,16 +1900,25 @@
       <c r="AF19"/>
       <c r="AG19"/>
       <c r="AH19"/>
-    </row>
-    <row r="20" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="43"/>
-      <c r="B20" s="55"/>
-      <c r="C20" s="47"/>
-      <c r="D20" s="47"/>
-      <c r="E20" s="47"/>
-      <c r="F20" s="47"/>
-      <c r="G20" s="47"/>
-      <c r="H20" s="14"/>
+      <c r="AI19"/>
+      <c r="AJ19"/>
+      <c r="AK19"/>
+      <c r="AL19"/>
+      <c r="AM19"/>
+      <c r="AN19"/>
+      <c r="AO19"/>
+      <c r="AP19"/>
+      <c r="AQ19"/>
+    </row>
+    <row r="20" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="35"/>
+      <c r="B20" s="36"/>
+      <c r="C20" s="54"/>
+      <c r="D20" s="54"/>
+      <c r="E20" s="54"/>
+      <c r="F20" s="54"/>
+      <c r="G20" s="54"/>
+      <c r="H20" s="55"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1862,8 +1945,25 @@
       <c r="AF20"/>
       <c r="AG20"/>
       <c r="AH20"/>
-    </row>
-    <row r="21" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AI20"/>
+      <c r="AJ20"/>
+      <c r="AK20"/>
+      <c r="AL20"/>
+      <c r="AM20"/>
+      <c r="AN20"/>
+      <c r="AO20"/>
+      <c r="AP20"/>
+      <c r="AQ20"/>
+    </row>
+    <row r="21" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21"/>
+      <c r="B21"/>
+      <c r="C21"/>
+      <c r="D21"/>
+      <c r="E21"/>
+      <c r="F21"/>
+      <c r="G21"/>
+      <c r="H21"/>
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -1890,8 +1990,25 @@
       <c r="AF21"/>
       <c r="AG21"/>
       <c r="AH21"/>
-    </row>
-    <row r="22" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI21"/>
+      <c r="AJ21"/>
+      <c r="AK21"/>
+      <c r="AL21"/>
+      <c r="AM21"/>
+      <c r="AN21"/>
+      <c r="AO21"/>
+      <c r="AP21"/>
+      <c r="AQ21"/>
+    </row>
+    <row r="22" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22"/>
+      <c r="B22"/>
+      <c r="C22"/>
+      <c r="D22"/>
+      <c r="E22"/>
+      <c r="F22"/>
+      <c r="G22"/>
+      <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -1918,8 +2035,17 @@
       <c r="AF22"/>
       <c r="AG22"/>
       <c r="AH22"/>
-    </row>
-    <row r="23" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI22"/>
+      <c r="AJ22"/>
+      <c r="AK22"/>
+      <c r="AL22"/>
+      <c r="AM22"/>
+      <c r="AN22"/>
+      <c r="AO22"/>
+      <c r="AP22"/>
+      <c r="AQ22"/>
+    </row>
+    <row r="23" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23"/>
@@ -1954,16 +2080,25 @@
       <c r="AF23"/>
       <c r="AG23"/>
       <c r="AH23"/>
-    </row>
-    <row r="24" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24"/>
-      <c r="B24"/>
-      <c r="C24"/>
-      <c r="D24"/>
-      <c r="E24"/>
-      <c r="F24"/>
-      <c r="G24"/>
-      <c r="H24"/>
+      <c r="AI23"/>
+      <c r="AJ23"/>
+      <c r="AK23"/>
+      <c r="AL23"/>
+      <c r="AM23"/>
+      <c r="AN23"/>
+      <c r="AO23"/>
+      <c r="AP23"/>
+      <c r="AQ23"/>
+    </row>
+    <row r="24" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="10"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -1990,8 +2125,17 @@
       <c r="AF24"/>
       <c r="AG24"/>
       <c r="AH24"/>
-    </row>
-    <row r="25" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI24"/>
+      <c r="AJ24"/>
+      <c r="AK24"/>
+      <c r="AL24"/>
+      <c r="AM24"/>
+      <c r="AN24"/>
+      <c r="AO24"/>
+      <c r="AP24"/>
+      <c r="AQ24"/>
+    </row>
+    <row r="25" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25"/>
@@ -2026,16 +2170,25 @@
       <c r="AF25"/>
       <c r="AG25"/>
       <c r="AH25"/>
-    </row>
-    <row r="26" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="10"/>
-      <c r="B26" s="11"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
-      <c r="H26" s="12"/>
+      <c r="AI25"/>
+      <c r="AJ25"/>
+      <c r="AK25"/>
+      <c r="AL25"/>
+      <c r="AM25"/>
+      <c r="AN25"/>
+      <c r="AO25"/>
+      <c r="AP25"/>
+      <c r="AQ25"/>
+    </row>
+    <row r="26" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26"/>
+      <c r="B26"/>
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2062,8 +2215,17 @@
       <c r="AF26"/>
       <c r="AG26"/>
       <c r="AH26"/>
-    </row>
-    <row r="27" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI26"/>
+      <c r="AJ26"/>
+      <c r="AK26"/>
+      <c r="AL26"/>
+      <c r="AM26"/>
+      <c r="AN26"/>
+      <c r="AO26"/>
+      <c r="AP26"/>
+      <c r="AQ26"/>
+    </row>
+    <row r="27" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -2098,8 +2260,17 @@
       <c r="AF27"/>
       <c r="AG27"/>
       <c r="AH27"/>
-    </row>
-    <row r="28" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI27"/>
+      <c r="AJ27"/>
+      <c r="AK27"/>
+      <c r="AL27"/>
+      <c r="AM27"/>
+      <c r="AN27"/>
+      <c r="AO27"/>
+      <c r="AP27"/>
+      <c r="AQ27"/>
+    </row>
+    <row r="28" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28"/>
@@ -2134,8 +2305,17 @@
       <c r="AF28"/>
       <c r="AG28"/>
       <c r="AH28"/>
-    </row>
-    <row r="29" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="AI28"/>
+      <c r="AJ28"/>
+      <c r="AK28"/>
+      <c r="AL28"/>
+      <c r="AM28"/>
+      <c r="AN28"/>
+      <c r="AO28"/>
+      <c r="AP28"/>
+      <c r="AQ28"/>
+    </row>
+    <row r="29" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -2170,8 +2350,17 @@
       <c r="AF29"/>
       <c r="AG29"/>
       <c r="AH29"/>
-    </row>
-    <row r="30" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI29"/>
+      <c r="AJ29"/>
+      <c r="AK29"/>
+      <c r="AL29"/>
+      <c r="AM29"/>
+      <c r="AN29"/>
+      <c r="AO29"/>
+      <c r="AP29"/>
+      <c r="AQ29"/>
+    </row>
+    <row r="30" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30"/>
@@ -2206,8 +2395,17 @@
       <c r="AF30"/>
       <c r="AG30"/>
       <c r="AH30"/>
-    </row>
-    <row r="31" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI30"/>
+      <c r="AJ30"/>
+      <c r="AK30"/>
+      <c r="AL30"/>
+      <c r="AM30"/>
+      <c r="AN30"/>
+      <c r="AO30"/>
+      <c r="AP30"/>
+      <c r="AQ30"/>
+    </row>
+    <row r="31" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31"/>
@@ -2242,8 +2440,17 @@
       <c r="AF31"/>
       <c r="AG31"/>
       <c r="AH31"/>
-    </row>
-    <row r="32" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="AI31"/>
+      <c r="AJ31"/>
+      <c r="AK31"/>
+      <c r="AL31"/>
+      <c r="AM31"/>
+      <c r="AN31"/>
+      <c r="AO31"/>
+      <c r="AP31"/>
+      <c r="AQ31"/>
+    </row>
+    <row r="32" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32"/>
@@ -2271,15 +2478,8 @@
       <c r="Y32"/>
       <c r="Z32"/>
       <c r="AA32"/>
-      <c r="AB32"/>
-      <c r="AC32"/>
-      <c r="AD32"/>
-      <c r="AE32"/>
-      <c r="AF32"/>
-      <c r="AG32"/>
-      <c r="AH32"/>
-    </row>
-    <row r="33" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="33" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33"/>
@@ -2307,15 +2507,8 @@
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
-      <c r="AB33"/>
-      <c r="AC33"/>
-      <c r="AD33"/>
-      <c r="AE33"/>
-      <c r="AF33"/>
-      <c r="AG33"/>
-      <c r="AH33"/>
-    </row>
-    <row r="34" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="34" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34"/>
@@ -2334,8 +2527,17 @@
       <c r="P34"/>
       <c r="Q34"/>
       <c r="R34"/>
-    </row>
-    <row r="35" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="S34"/>
+      <c r="T34"/>
+      <c r="U34"/>
+      <c r="V34"/>
+      <c r="W34"/>
+      <c r="X34"/>
+      <c r="Y34"/>
+      <c r="Z34"/>
+      <c r="AA34"/>
+    </row>
+    <row r="35" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -2354,74 +2556,45 @@
       <c r="P35"/>
       <c r="Q35"/>
       <c r="R35"/>
-    </row>
-    <row r="36" spans="1:34" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36"/>
-      <c r="B36"/>
-      <c r="C36"/>
-      <c r="D36"/>
-      <c r="E36"/>
-      <c r="F36"/>
-      <c r="G36"/>
-      <c r="H36"/>
-      <c r="I36"/>
-      <c r="J36"/>
-      <c r="K36"/>
-      <c r="L36"/>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
-      <c r="P36"/>
-      <c r="Q36"/>
-      <c r="R36"/>
-    </row>
-    <row r="37" spans="1:34" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37"/>
-      <c r="D37"/>
-      <c r="E37"/>
-      <c r="F37"/>
-      <c r="G37"/>
-      <c r="H37"/>
-      <c r="I37"/>
-      <c r="J37"/>
-      <c r="K37"/>
-      <c r="L37"/>
-      <c r="M37"/>
-      <c r="N37"/>
-      <c r="O37"/>
-      <c r="P37"/>
-      <c r="Q37"/>
-      <c r="R37"/>
-      <c r="S37"/>
-      <c r="T37"/>
-      <c r="U37"/>
-      <c r="V37"/>
-      <c r="W37"/>
-      <c r="X37"/>
-      <c r="Y37"/>
-      <c r="Z37"/>
-      <c r="AA37"/>
-      <c r="AB37"/>
-      <c r="AC37"/>
-      <c r="AD37"/>
-      <c r="AE37"/>
-      <c r="AF37"/>
-      <c r="AG37"/>
-      <c r="AH37"/>
-    </row>
-    <row r="38" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="39" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="40" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="41" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="42" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="43" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="44" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="45" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="46" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="47" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="48" spans="1:34" customFormat="1" x14ac:dyDescent="0.2"/>
+      <c r="S35"/>
+      <c r="T35"/>
+      <c r="U35"/>
+      <c r="V35"/>
+      <c r="W35"/>
+      <c r="X35"/>
+      <c r="Y35"/>
+      <c r="Z35"/>
+      <c r="AA35"/>
+      <c r="AB35"/>
+      <c r="AC35"/>
+      <c r="AD35"/>
+      <c r="AE35"/>
+      <c r="AF35"/>
+      <c r="AG35"/>
+      <c r="AH35"/>
+      <c r="AI35"/>
+      <c r="AJ35"/>
+      <c r="AK35"/>
+      <c r="AL35"/>
+      <c r="AM35"/>
+      <c r="AN35"/>
+      <c r="AO35"/>
+      <c r="AP35"/>
+      <c r="AQ35"/>
+    </row>
+    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="41" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="43" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="44" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="46" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="47" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="48" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="49" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="50" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="51" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2444,8 +2617,26 @@
     <row r="68" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="69" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+    </row>
+    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+    </row>
     <row r="73" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
@@ -2536,64 +2727,24 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
-    <row r="82" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
-      <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
-      <c r="H82" s="1"/>
-    </row>
-    <row r="83" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-    </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="E16:E17"/>
-    <mergeCell ref="F16:F17"/>
-    <mergeCell ref="G16:G17"/>
-    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="F17:F18"/>
+    <mergeCell ref="G17:G18"/>
+    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="A19:A20"/>
+    <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
     <mergeCell ref="G19:G20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="B19:B20"/>
-    <mergeCell ref="A19:A20"/>
-    <mergeCell ref="A18:H18"/>
-    <mergeCell ref="A14:A15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B14:B15"/>
-    <mergeCell ref="C14:C15"/>
-    <mergeCell ref="D14:D15"/>
-    <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
     <mergeCell ref="H19:H20"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A17:A18"/>
+    <mergeCell ref="B17:B18"/>
+    <mergeCell ref="C17:C18"/>
+    <mergeCell ref="D17:D18"/>
+    <mergeCell ref="E17:E18"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
@@ -2610,6 +2761,26 @@
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="B14:B15"/>
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078738" right="0.19685039370078738" top="0.19685039370078738" bottom="0.19685039370078738" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2627,16 +2798,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944753b-810f-46c8-bac0-e8d58c60cb9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010056620F2C176D974991F270E01E69A174" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="c1041e1bc637f9a452b3a666f0dfb4c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c944753b-810f-46c8-bac0-e8d58c60cb9e" xmlns:ns3="4de7a12e-8c42-4030-a9c5-072174f335a6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3c11a7b616be7a4861d8d8f26cc3a83b" ns2:_="" ns3:_="">
     <xsd:import namespace="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
@@ -2853,6 +3014,16 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944753b-810f-46c8-bac0-e8d58c60cb9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C2B63-1469-46C2-8035-1ACD6A901C28}">
   <ds:schemaRefs>
@@ -2862,16 +3033,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DA88B-CC83-4B6A-8FB8-D09E146481DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A1580AE-FEAE-4C59-8F8B-C5B5168C8CA5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2888,4 +3049,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DA88B-CC83-4B6A-8FB8-D09E146481DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
+++ b/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hugo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A4F9A8B-8342-4978-94A7-3FD880638099}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FA2F24-3C3D-495F-96EC-E61E5696C246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Tableau de synthèse Épreuve E5" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Tableau de synthèse Épreuve E5'!$A$1:$H$26</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -813,6 +813,120 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -830,120 +944,6 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1178,7 +1178,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AQ81"/>
+  <dimension ref="A1:AQ83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="70.42578125" style="1" customWidth="1"/>
@@ -1189,56 +1189,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13" t="s">
+      <c r="B1" s="51"/>
+      <c r="C1" s="51"/>
+      <c r="D1" s="51"/>
+      <c r="E1" s="51"/>
+      <c r="F1" s="51"/>
+      <c r="G1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="13"/>
+      <c r="H1" s="51"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="51"/>
+      <c r="E2" s="51"/>
+      <c r="F2" s="51"/>
+      <c r="G2" s="51"/>
+      <c r="H2" s="51"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="17" t="s">
+      <c r="B3" s="53"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="54"/>
+      <c r="F3" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="18"/>
+      <c r="G3" s="53"/>
+      <c r="H3" s="56"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="24"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
+      <c r="E4" s="39"/>
       <c r="F4" s="2" t="s">
         <v>4</v>
       </c>
@@ -1250,22 +1250,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="25" t="s">
+      <c r="A5" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="27"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
+      <c r="F5" s="41"/>
+      <c r="G5" s="41"/>
+      <c r="H5" s="42"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="28" t="s">
+      <c r="A6" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="45" t="s">
         <v>7</v>
       </c>
       <c r="C6" s="5" t="s">
@@ -1288,8 +1288,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="29"/>
-      <c r="B7" s="31"/>
+      <c r="A7" s="44"/>
+      <c r="B7" s="46"/>
       <c r="C7" s="8" t="s">
         <v>14</v>
       </c>
@@ -1345,16 +1345,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
-      <c r="F8" s="39"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="40"/>
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="50"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1392,18 +1392,18 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="37" t="s">
+      <c r="A9" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="43"/>
-      <c r="G9" s="43"/>
-      <c r="H9" s="43"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1441,14 +1441,14 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="38"/>
-      <c r="B10" s="47"/>
-      <c r="C10" s="42"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="44"/>
-      <c r="G10" s="44"/>
-      <c r="H10" s="44"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="27"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="23"/>
+      <c r="F10" s="23"/>
+      <c r="G10" s="23"/>
+      <c r="H10" s="23"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1486,18 +1486,18 @@
       <c r="AQ10"/>
     </row>
     <row r="11" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="34" t="s">
+      <c r="A11" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="45" t="s">
+      <c r="B11" s="21" t="s">
         <v>32</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="52"/>
-      <c r="G11" s="52"/>
-      <c r="H11" s="53"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="25"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1535,14 +1535,14 @@
       <c r="AQ11"/>
     </row>
     <row r="12" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="35"/>
-      <c r="B12" s="36"/>
-      <c r="C12" s="54"/>
-      <c r="D12" s="54"/>
-      <c r="E12" s="54"/>
-      <c r="F12" s="54"/>
-      <c r="G12" s="54"/>
-      <c r="H12" s="55"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="14"/>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14"/>
+      <c r="G12" s="14"/>
+      <c r="H12" s="16"/>
       <c r="I12"/>
       <c r="J12"/>
       <c r="K12"/>
@@ -1580,16 +1580,16 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="19" t="s">
+      <c r="A13" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B13" s="20"/>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="21"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="36"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1627,18 +1627,18 @@
       <c r="AQ13"/>
     </row>
     <row r="14" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="34" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="C14" s="51"/>
-      <c r="D14" s="51"/>
-      <c r="E14" s="51"/>
-      <c r="F14" s="51"/>
-      <c r="G14" s="51"/>
-      <c r="H14" s="56"/>
+      <c r="A14" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="15"/>
       <c r="I14"/>
       <c r="J14"/>
       <c r="K14"/>
@@ -1676,14 +1676,14 @@
       <c r="AQ14"/>
     </row>
     <row r="15" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="54"/>
-      <c r="D15" s="54"/>
-      <c r="E15" s="54"/>
-      <c r="F15" s="54"/>
-      <c r="G15" s="54"/>
-      <c r="H15" s="55"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="16"/>
       <c r="I15"/>
       <c r="J15"/>
       <c r="K15"/>
@@ -1721,27 +1721,21 @@
       <c r="AQ15"/>
     </row>
     <row r="16" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B16" s="20"/>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="21"/>
+      <c r="A16" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="15"/>
       <c r="I16"/>
       <c r="J16"/>
       <c r="K16"/>
-      <c r="L16"/>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-      <c r="P16"/>
-      <c r="Q16"/>
-      <c r="R16"/>
-      <c r="S16"/>
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16"/>
@@ -1768,29 +1762,17 @@
       <c r="AQ16"/>
     </row>
     <row r="17" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="34" t="s">
-        <v>30</v>
-      </c>
-      <c r="B17" s="45" t="s">
-        <v>34</v>
-      </c>
-      <c r="C17" s="51"/>
-      <c r="D17" s="51"/>
-      <c r="E17" s="51"/>
-      <c r="F17" s="51"/>
-      <c r="G17" s="51"/>
-      <c r="H17" s="56"/>
+      <c r="A17" s="18"/>
+      <c r="B17" s="20"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="16"/>
       <c r="I17"/>
       <c r="J17"/>
       <c r="K17"/>
-      <c r="L17"/>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
-      <c r="P17"/>
-      <c r="Q17"/>
-      <c r="R17"/>
-      <c r="S17"/>
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17"/>
@@ -1817,14 +1799,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="35"/>
-      <c r="B18" s="36"/>
-      <c r="C18" s="54"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="54"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
-      <c r="H18" s="55"/>
+      <c r="A18" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="35"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="35"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="36"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1861,19 +1845,19 @@
       <c r="AP18"/>
       <c r="AQ18"/>
     </row>
-    <row r="19" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34" t="s">
-        <v>31</v>
-      </c>
-      <c r="B19" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="51"/>
-      <c r="D19" s="51"/>
-      <c r="E19" s="51"/>
-      <c r="F19" s="51"/>
-      <c r="G19" s="51"/>
-      <c r="H19" s="56"/>
+    <row r="19" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
+      <c r="H19" s="15"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1911,14 +1895,14 @@
       <c r="AQ19"/>
     </row>
     <row r="20" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="35"/>
-      <c r="B20" s="36"/>
-      <c r="C20" s="54"/>
-      <c r="D20" s="54"/>
-      <c r="E20" s="54"/>
-      <c r="F20" s="54"/>
-      <c r="G20" s="54"/>
-      <c r="H20" s="55"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="16"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -1955,15 +1939,7 @@
       <c r="AP20"/>
       <c r="AQ20"/>
     </row>
-    <row r="21" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21"/>
-      <c r="D21"/>
-      <c r="E21"/>
-      <c r="F21"/>
-      <c r="G21"/>
-      <c r="H21"/>
+    <row r="21" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="I21"/>
       <c r="J21"/>
       <c r="K21"/>
@@ -2001,14 +1977,6 @@
       <c r="AQ21"/>
     </row>
     <row r="22" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22"/>
-      <c r="D22"/>
-      <c r="E22"/>
-      <c r="F22"/>
-      <c r="G22"/>
-      <c r="H22"/>
       <c r="I22"/>
       <c r="J22"/>
       <c r="K22"/>
@@ -2091,14 +2059,14 @@
       <c r="AQ23"/>
     </row>
     <row r="24" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="10"/>
-      <c r="B24" s="11"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
-      <c r="H24" s="12"/>
+      <c r="A24"/>
+      <c r="B24"/>
+      <c r="C24"/>
+      <c r="D24"/>
+      <c r="E24"/>
+      <c r="F24"/>
+      <c r="G24"/>
+      <c r="H24"/>
       <c r="I24"/>
       <c r="J24"/>
       <c r="K24"/>
@@ -2181,14 +2149,14 @@
       <c r="AQ25"/>
     </row>
     <row r="26" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
+      <c r="A26" s="10"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
       <c r="I26"/>
       <c r="J26"/>
       <c r="K26"/>
@@ -2225,7 +2193,7 @@
       <c r="AP26"/>
       <c r="AQ26"/>
     </row>
-    <row r="27" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27"/>
@@ -2315,7 +2283,7 @@
       <c r="AP28"/>
       <c r="AQ28"/>
     </row>
-    <row r="29" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29"/>
@@ -2478,6 +2446,22 @@
       <c r="Y32"/>
       <c r="Z32"/>
       <c r="AA32"/>
+      <c r="AB32"/>
+      <c r="AC32"/>
+      <c r="AD32"/>
+      <c r="AE32"/>
+      <c r="AF32"/>
+      <c r="AG32"/>
+      <c r="AH32"/>
+      <c r="AI32"/>
+      <c r="AJ32"/>
+      <c r="AK32"/>
+      <c r="AL32"/>
+      <c r="AM32"/>
+      <c r="AN32"/>
+      <c r="AO32"/>
+      <c r="AP32"/>
+      <c r="AQ32"/>
     </row>
     <row r="33" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33"/>
@@ -2507,6 +2491,22 @@
       <c r="Y33"/>
       <c r="Z33"/>
       <c r="AA33"/>
+      <c r="AB33"/>
+      <c r="AC33"/>
+      <c r="AD33"/>
+      <c r="AE33"/>
+      <c r="AF33"/>
+      <c r="AG33"/>
+      <c r="AH33"/>
+      <c r="AI33"/>
+      <c r="AJ33"/>
+      <c r="AK33"/>
+      <c r="AL33"/>
+      <c r="AM33"/>
+      <c r="AN33"/>
+      <c r="AO33"/>
+      <c r="AP33"/>
+      <c r="AQ33"/>
     </row>
     <row r="34" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34"/>
@@ -2537,7 +2537,7 @@
       <c r="Z34"/>
       <c r="AA34"/>
     </row>
-    <row r="35" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35"/>
@@ -2565,25 +2565,81 @@
       <c r="Y35"/>
       <c r="Z35"/>
       <c r="AA35"/>
-      <c r="AB35"/>
-      <c r="AC35"/>
-      <c r="AD35"/>
-      <c r="AE35"/>
-      <c r="AF35"/>
-      <c r="AG35"/>
-      <c r="AH35"/>
-      <c r="AI35"/>
-      <c r="AJ35"/>
-      <c r="AK35"/>
-      <c r="AL35"/>
-      <c r="AM35"/>
-      <c r="AN35"/>
-      <c r="AO35"/>
-      <c r="AP35"/>
-      <c r="AQ35"/>
-    </row>
-    <row r="36" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="37" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
+    </row>
+    <row r="36" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36"/>
+      <c r="B36"/>
+      <c r="C36"/>
+      <c r="D36"/>
+      <c r="E36"/>
+      <c r="F36"/>
+      <c r="G36"/>
+      <c r="H36"/>
+      <c r="I36"/>
+      <c r="J36"/>
+      <c r="K36"/>
+      <c r="L36"/>
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+      <c r="P36"/>
+      <c r="Q36"/>
+      <c r="R36"/>
+      <c r="S36"/>
+      <c r="T36"/>
+      <c r="U36"/>
+      <c r="V36"/>
+      <c r="W36"/>
+      <c r="X36"/>
+      <c r="Y36"/>
+      <c r="Z36"/>
+      <c r="AA36"/>
+    </row>
+    <row r="37" spans="1:43" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37"/>
+      <c r="B37"/>
+      <c r="C37"/>
+      <c r="D37"/>
+      <c r="E37"/>
+      <c r="F37"/>
+      <c r="G37"/>
+      <c r="H37"/>
+      <c r="I37"/>
+      <c r="J37"/>
+      <c r="K37"/>
+      <c r="L37"/>
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+      <c r="P37"/>
+      <c r="Q37"/>
+      <c r="R37"/>
+      <c r="S37"/>
+      <c r="T37"/>
+      <c r="U37"/>
+      <c r="V37"/>
+      <c r="W37"/>
+      <c r="X37"/>
+      <c r="Y37"/>
+      <c r="Z37"/>
+      <c r="AA37"/>
+      <c r="AB37"/>
+      <c r="AC37"/>
+      <c r="AD37"/>
+      <c r="AE37"/>
+      <c r="AF37"/>
+      <c r="AG37"/>
+      <c r="AH37"/>
+      <c r="AI37"/>
+      <c r="AJ37"/>
+      <c r="AK37"/>
+      <c r="AL37"/>
+      <c r="AM37"/>
+      <c r="AN37"/>
+      <c r="AO37"/>
+      <c r="AP37"/>
+      <c r="AQ37"/>
+    </row>
     <row r="38" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="39" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="40" spans="1:43" customFormat="1" x14ac:dyDescent="0.2"/>
@@ -2617,26 +2673,8 @@
     <row r="68" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="69" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="70" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
-    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-    </row>
-    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-    </row>
+    <row r="71" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
+    <row r="72" spans="1:8" customFormat="1" x14ac:dyDescent="0.2"/>
     <row r="73" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
@@ -2727,11 +2765,40 @@
       <c r="G81" s="1"/>
       <c r="H81" s="1"/>
     </row>
+    <row r="82" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+    </row>
+    <row r="83" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="F17:F18"/>
-    <mergeCell ref="G17:G18"/>
-    <mergeCell ref="H17:H18"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:H3"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
@@ -2740,11 +2807,6 @@
     <mergeCell ref="F19:F20"/>
     <mergeCell ref="G19:G20"/>
     <mergeCell ref="H19:H20"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="B17:B18"/>
-    <mergeCell ref="C17:C18"/>
-    <mergeCell ref="D17:D18"/>
-    <mergeCell ref="E17:E18"/>
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
@@ -2761,26 +2823,22 @@
     <mergeCell ref="A9:A10"/>
     <mergeCell ref="D9:D10"/>
     <mergeCell ref="E9:E10"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A5:H5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A8:H8"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="G16:G17"/>
+    <mergeCell ref="H16:H17"/>
     <mergeCell ref="A14:A15"/>
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E14:E15"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078738" right="0.19685039370078738" top="0.19685039370078738" bottom="0.19685039370078738" header="0.51181102362204722" footer="0.51181102362204722"/>
@@ -2798,6 +2856,16 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944753b-810f-46c8-bac0-e8d58c60cb9e">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010056620F2C176D974991F270E01E69A174" ma:contentTypeVersion="13" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="c1041e1bc637f9a452b3a666f0dfb4c6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c944753b-810f-46c8-bac0-e8d58c60cb9e" xmlns:ns3="4de7a12e-8c42-4030-a9c5-072174f335a6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3c11a7b616be7a4861d8d8f26cc3a83b" ns2:_="" ns3:_="">
     <xsd:import namespace="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
@@ -3014,16 +3082,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="c944753b-810f-46c8-bac0-e8d58c60cb9e">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{494C2B63-1469-46C2-8035-1ACD6A901C28}">
   <ds:schemaRefs>
@@ -3033,6 +3091,23 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DA88B-CC83-4B6A-8FB8-D09E146481DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="4de7a12e-8c42-4030-a9c5-072174f335a6"/>
+    <ds:schemaRef ds:uri="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8A1580AE-FEAE-4C59-8F8B-C5B5168C8CA5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3049,14 +3124,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2E0DA88B-CC83-4B6A-8FB8-D09E146481DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="c944753b-810f-46c8-bac0-e8d58c60cb9e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
+++ b/Tableau_synthese_ALMAZAN-LAFORET_Hugo_2026.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hugo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03FA2F24-3C3D-495F-96EC-E61E5696C246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F32AE6F4-1CCA-43D7-9940-E5D30C1D1E7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -50,9 +50,6 @@
     <t xml:space="preserve">Tableau de synthèse des réalisations professionnelles </t>
   </si>
   <si>
-    <t xml:space="preserve">N° candidat : </t>
-  </si>
-  <si>
     <t>Option :</t>
   </si>
   <si>
@@ -135,9 +132,6 @@
     <t>Centre de formation : Lycée Joseph-Marie Carriat</t>
   </si>
   <si>
-    <t>Adresse URL du portfolio : http://135.125.103.97/portfolio/</t>
-  </si>
-  <si>
     <t>☑ SLAM</t>
   </si>
   <si>
@@ -162,11 +156,6 @@
 ?</t>
   </si>
   <si>
-    <t>12/01/2026 
-au
-?</t>
-  </si>
-  <si>
     <t>26/05/2025 
 au
 04/07/2025</t>
@@ -175,6 +164,17 @@
     <t>04/07/2025
 au
 26/08/2025</t>
+  </si>
+  <si>
+    <t>12/01/2026 
+au
+27/02/2026</t>
+  </si>
+  <si>
+    <t>Adresse URL du portfolio : https://hugoal.fr</t>
+  </si>
+  <si>
+    <t>N° candidat : 2149109938</t>
   </si>
 </sst>
 </file>
@@ -184,7 +184,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-* #,##0.00\ [$€-1]_-;\-* #,##0.00\ [$€-1]_-;_-* &quot;-&quot;??\ [$€-1]_-"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -235,8 +235,14 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,6 +255,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="41">
     <border>
@@ -775,7 +787,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -819,10 +831,10 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -831,26 +843,65 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="9" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -858,10 +909,10 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -870,80 +921,68 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1189,124 +1228,124 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="51"/>
-      <c r="C1" s="51"/>
-      <c r="D1" s="51"/>
-      <c r="E1" s="51"/>
-      <c r="F1" s="51"/>
-      <c r="G1" s="51" t="s">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+      <c r="G1" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="H1" s="51"/>
+      <c r="H1" s="33"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="51" t="s">
+      <c r="A2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="33"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
     </row>
     <row r="3" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="54"/>
-      <c r="F3" s="55" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="53"/>
-      <c r="H3" s="56"/>
+      <c r="A3" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="35"/>
+      <c r="C3" s="35"/>
+      <c r="D3" s="35"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="35"/>
+      <c r="H3" s="38"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="45" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="46"/>
+      <c r="C4" s="46"/>
+      <c r="D4" s="46"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
-      <c r="E4" s="39"/>
-      <c r="F4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="48" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
+      <c r="E5" s="49"/>
+      <c r="F5" s="49"/>
+      <c r="G5" s="49"/>
+      <c r="H5" s="50"/>
+    </row>
+    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:43" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="41"/>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="41"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-    </row>
-    <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="43" t="s">
+      <c r="B6" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="45" t="s">
+      <c r="C6" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="G6" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="H6" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="6" t="s">
+    </row>
+    <row r="7" spans="1:43" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="52"/>
+      <c r="B7" s="54"/>
+      <c r="C7" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="7" spans="1:43" s="7" customFormat="1" ht="324.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="44"/>
-      <c r="B7" s="46"/>
-      <c r="C7" s="8" t="s">
+      <c r="D7" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="E7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="F7" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="G7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="H7" s="9" t="s">
         <v>18</v>
-      </c>
-      <c r="H7" s="9" t="s">
-        <v>19</v>
       </c>
       <c r="I7"/>
       <c r="J7"/>
@@ -1345,16 +1384,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="7" customFormat="1" ht="18" x14ac:dyDescent="0.2">
-      <c r="A8" s="47" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="50"/>
+      <c r="A8" s="55" t="s">
+        <v>19</v>
+      </c>
+      <c r="B8" s="56"/>
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="58"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1392,18 +1431,18 @@
       <c r="AQ8"/>
     </row>
     <row r="9" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="B9" s="26" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
+      <c r="A9" s="43" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9" s="39" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="41"/>
+      <c r="D9" s="64"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="26"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="26"/>
       <c r="I9"/>
       <c r="J9"/>
       <c r="K9"/>
@@ -1441,14 +1480,14 @@
       <c r="AQ9"/>
     </row>
     <row r="10" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="31"/>
-      <c r="B10" s="27"/>
-      <c r="C10" s="29"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="23"/>
-      <c r="F10" s="23"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="23"/>
+      <c r="A10" s="44"/>
+      <c r="B10" s="40"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="65"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="27"/>
       <c r="I10"/>
       <c r="J10"/>
       <c r="K10"/>
@@ -1487,17 +1526,17 @@
     </row>
     <row r="11" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="17" t="s">
-        <v>28</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" s="24"/>
-      <c r="G11" s="24"/>
-      <c r="H11" s="25"/>
+        <v>26</v>
+      </c>
+      <c r="B11" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="21"/>
+      <c r="D11" s="60"/>
+      <c r="E11" s="28"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="29"/>
       <c r="I11"/>
       <c r="J11"/>
       <c r="K11"/>
@@ -1537,10 +1576,10 @@
     <row r="12" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="18"/>
       <c r="B12" s="20"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="14"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="61"/>
       <c r="E12" s="14"/>
-      <c r="F12" s="14"/>
+      <c r="F12" s="22"/>
       <c r="G12" s="14"/>
       <c r="H12" s="16"/>
       <c r="I12"/>
@@ -1580,16 +1619,16 @@
       <c r="AQ12"/>
     </row>
     <row r="13" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="34" t="s">
-        <v>21</v>
-      </c>
-      <c r="B13" s="35"/>
-      <c r="C13" s="35"/>
-      <c r="D13" s="35"/>
-      <c r="E13" s="35"/>
-      <c r="F13" s="35"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="36"/>
+      <c r="A13" s="30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="31"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="31"/>
+      <c r="H13" s="32"/>
       <c r="I13"/>
       <c r="J13"/>
       <c r="K13"/>
@@ -1628,14 +1667,14 @@
     </row>
     <row r="14" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="21" t="s">
-        <v>34</v>
+        <v>28</v>
+      </c>
+      <c r="B14" s="19" t="s">
+        <v>31</v>
       </c>
       <c r="C14" s="13"/>
       <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
+      <c r="E14" s="21"/>
       <c r="F14" s="13"/>
       <c r="G14" s="13"/>
       <c r="H14" s="15"/>
@@ -1680,7 +1719,7 @@
       <c r="B15" s="20"/>
       <c r="C15" s="14"/>
       <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
+      <c r="E15" s="22"/>
       <c r="F15" s="14"/>
       <c r="G15" s="14"/>
       <c r="H15" s="16"/>
@@ -1722,14 +1761,14 @@
     </row>
     <row r="16" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>35</v>
+        <v>29</v>
+      </c>
+      <c r="B16" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="C16" s="13"/>
       <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
+      <c r="E16" s="21"/>
       <c r="F16" s="13"/>
       <c r="G16" s="13"/>
       <c r="H16" s="15"/>
@@ -1766,13 +1805,12 @@
       <c r="B17" s="20"/>
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
+      <c r="E17" s="22"/>
       <c r="F17" s="14"/>
       <c r="G17" s="14"/>
       <c r="H17" s="16"/>
       <c r="I17"/>
       <c r="J17"/>
-      <c r="K17"/>
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17"/>
@@ -1799,16 +1837,16 @@
       <c r="AQ17"/>
     </row>
     <row r="18" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="35"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="35"/>
-      <c r="E18" s="35"/>
-      <c r="F18" s="35"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="36"/>
+      <c r="A18" s="30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="31"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="31"/>
+      <c r="H18" s="32"/>
       <c r="I18"/>
       <c r="J18"/>
       <c r="K18"/>
@@ -1847,17 +1885,17 @@
     </row>
     <row r="19" spans="1:43" s="7" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="B19" s="19" t="s">
         <v>33</v>
       </c>
       <c r="C19" s="13"/>
       <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
+      <c r="E19" s="21"/>
       <c r="F19" s="13"/>
       <c r="G19" s="13"/>
-      <c r="H19" s="15"/>
+      <c r="H19" s="62"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -1899,10 +1937,10 @@
       <c r="B20" s="20"/>
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
+      <c r="E20" s="22"/>
       <c r="F20" s="14"/>
       <c r="G20" s="14"/>
-      <c r="H20" s="16"/>
+      <c r="H20" s="63"/>
       <c r="I20"/>
       <c r="J20"/>
       <c r="K20"/>
@@ -2787,18 +2825,21 @@
     </row>
   </sheetData>
   <mergeCells count="52">
-    <mergeCell ref="A1:F1"/>
     <mergeCell ref="G1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="F3:H3"/>
-    <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A18:H18"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="A1:F1"/>
     <mergeCell ref="A4:E4"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A8:H8"/>
+    <mergeCell ref="E9:E10"/>
     <mergeCell ref="A19:A20"/>
     <mergeCell ref="B19:B20"/>
     <mergeCell ref="C19:C20"/>
@@ -2810,27 +2851,16 @@
     <mergeCell ref="F9:F10"/>
     <mergeCell ref="G9:G10"/>
     <mergeCell ref="H9:H10"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="G11:G12"/>
+    <mergeCell ref="H11:H12"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A18:H18"/>
     <mergeCell ref="A11:A12"/>
     <mergeCell ref="B11:B12"/>
     <mergeCell ref="C11:C12"/>
     <mergeCell ref="D11:D12"/>
     <mergeCell ref="E11:E12"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="G11:G12"/>
-    <mergeCell ref="H11:H12"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="F14:F15"/>
-    <mergeCell ref="G14:G15"/>
-    <mergeCell ref="H14:H15"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C16:C17"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="E16:E17"/>
     <mergeCell ref="F16:F17"/>
     <mergeCell ref="G16:G17"/>
     <mergeCell ref="H16:H17"/>
@@ -2838,7 +2868,15 @@
     <mergeCell ref="B14:B15"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="D14:D15"/>
+    <mergeCell ref="A16:A17"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="C16:C17"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="E14:E15"/>
+    <mergeCell ref="F14:F15"/>
+    <mergeCell ref="G14:G15"/>
+    <mergeCell ref="H14:H15"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.19685039370078738" right="0.19685039370078738" top="0.19685039370078738" bottom="0.19685039370078738" header="0.51181102362204722" footer="0.51181102362204722"/>
